--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260615.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260615.xlsx
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>3,772,678</t>
+          <t>8,198,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>8,198,000</t>
+          <t>3,772,678</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
